--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/37.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/37.xlsx
@@ -426,13 +426,13 @@
         <v>-20.85689610114364</v>
       </c>
       <c r="E2">
-        <v>-12.31736986503884</v>
+        <v>-13.19375185432126</v>
       </c>
       <c r="F2">
-        <v>1.382017946520031</v>
+        <v>2.003766635568319</v>
       </c>
       <c r="G2">
-        <v>-15.96584857600443</v>
+        <v>-18.19414367303247</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.17462646574065</v>
       </c>
       <c r="E3">
-        <v>-13.25923358847217</v>
+        <v>-12.52553022974942</v>
       </c>
       <c r="F3">
-        <v>1.656459928312449</v>
+        <v>2.065966685397204</v>
       </c>
       <c r="G3">
-        <v>-15.85048930614299</v>
+        <v>-18.95940772461763</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.39655767473858</v>
       </c>
       <c r="E4">
-        <v>-13.00653115342214</v>
+        <v>-13.15301823062226</v>
       </c>
       <c r="F4">
-        <v>1.276349920430081</v>
+        <v>2.367722843113205</v>
       </c>
       <c r="G4">
-        <v>-14.75560913266752</v>
+        <v>-15.90098340198072</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.59158349530747</v>
       </c>
       <c r="E5">
-        <v>-14.68322129713213</v>
+        <v>-13.88795786274911</v>
       </c>
       <c r="F5">
-        <v>1.215648056397202</v>
+        <v>2.053197264601015</v>
       </c>
       <c r="G5">
-        <v>-14.61218471299691</v>
+        <v>-17.3410425719266</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.76433113687413</v>
       </c>
       <c r="E6">
-        <v>-14.8169833623707</v>
+        <v>-14.3983440542576</v>
       </c>
       <c r="F6">
-        <v>1.605268218301784</v>
+        <v>2.739116133636994</v>
       </c>
       <c r="G6">
-        <v>-14.23314214620528</v>
+        <v>-15.88221426404582</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.94964583191488</v>
       </c>
       <c r="E7">
-        <v>-15.59069126047721</v>
+        <v>-15.22621250149585</v>
       </c>
       <c r="F7">
-        <v>1.771372045830819</v>
+        <v>2.486652822539046</v>
       </c>
       <c r="G7">
-        <v>-13.3285753041459</v>
+        <v>-15.52595983747377</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.15251262344116</v>
       </c>
       <c r="E8">
-        <v>-15.53291698908735</v>
+        <v>-15.63433216448913</v>
       </c>
       <c r="F8">
-        <v>1.632507960047342</v>
+        <v>2.460725972997387</v>
       </c>
       <c r="G8">
-        <v>-13.30338205259205</v>
+        <v>-14.57284053453544</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.3789823371154</v>
       </c>
       <c r="E9">
-        <v>-15.98387601619319</v>
+        <v>-16.32331231391213</v>
       </c>
       <c r="F9">
-        <v>1.871867688400945</v>
+        <v>2.222753571025709</v>
       </c>
       <c r="G9">
-        <v>-11.60991220852434</v>
+        <v>-14.08841171631943</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.63916322292072</v>
       </c>
       <c r="E10">
-        <v>-16.97110146376136</v>
+        <v>-17.70669772461931</v>
       </c>
       <c r="F10">
-        <v>1.793094156166987</v>
+        <v>2.492229051067308</v>
       </c>
       <c r="G10">
-        <v>-11.86903522897418</v>
+        <v>-13.43409232211909</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.93176382574656</v>
       </c>
       <c r="E11">
-        <v>-17.78133603321374</v>
+        <v>-16.77025458457316</v>
       </c>
       <c r="F11">
-        <v>1.828425051434525</v>
+        <v>2.655062525880961</v>
       </c>
       <c r="G11">
-        <v>-11.82458453401838</v>
+        <v>-13.23442338900903</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.25305574100344</v>
       </c>
       <c r="E12">
-        <v>-18.63156608510186</v>
+        <v>-16.60334861807245</v>
       </c>
       <c r="F12">
-        <v>1.573427810871874</v>
+        <v>2.622713748852195</v>
       </c>
       <c r="G12">
-        <v>-10.94492292605094</v>
+        <v>-12.78100114031383</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.58801386521983</v>
       </c>
       <c r="E13">
-        <v>-18.84959399467516</v>
+        <v>-20.27393492430772</v>
       </c>
       <c r="F13">
-        <v>1.997973439329642</v>
+        <v>2.651112763327855</v>
       </c>
       <c r="G13">
-        <v>-10.51387996520121</v>
+        <v>-12.57443634084547</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.94441163476141</v>
       </c>
       <c r="E14">
-        <v>-20.11431980095936</v>
+        <v>-20.86763598060933</v>
       </c>
       <c r="F14">
-        <v>2.253681763848326</v>
+        <v>2.993709529191209</v>
       </c>
       <c r="G14">
-        <v>-9.99511747919742</v>
+        <v>-12.0129446435663</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.30937520440385</v>
       </c>
       <c r="E15">
-        <v>-20.85738351545596</v>
+        <v>-21.00022517107991</v>
       </c>
       <c r="F15">
-        <v>2.119583049164406</v>
+        <v>2.966826121276624</v>
       </c>
       <c r="G15">
-        <v>-10.2949271043249</v>
+        <v>-11.68702474577059</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.67083943383957</v>
       </c>
       <c r="E16">
-        <v>-22.45501555994004</v>
+        <v>-22.03759441133501</v>
       </c>
       <c r="F16">
-        <v>2.599906799963952</v>
+        <v>3.559542313483077</v>
       </c>
       <c r="G16">
-        <v>-8.678943889149375</v>
+        <v>-11.29225212184912</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.02493690766608</v>
       </c>
       <c r="E17">
-        <v>-22.17649629457228</v>
+        <v>-24.08372199306476</v>
       </c>
       <c r="F17">
-        <v>2.451797039046139</v>
+        <v>3.094027796698806</v>
       </c>
       <c r="G17">
-        <v>-8.566729637550239</v>
+        <v>-11.06628090442955</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.372715372684439</v>
       </c>
       <c r="E18">
-        <v>-25.198514553429</v>
+        <v>-24.21974829530716</v>
       </c>
       <c r="F18">
-        <v>3.18554699414022</v>
+        <v>3.609166154637456</v>
       </c>
       <c r="G18">
-        <v>-8.721656547697052</v>
+        <v>-10.16335940350318</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.711892289207242</v>
       </c>
       <c r="E19">
-        <v>-24.63797551228555</v>
+        <v>-23.85517443837164</v>
       </c>
       <c r="F19">
-        <v>3.016796794026485</v>
+        <v>4.004639693605503</v>
       </c>
       <c r="G19">
-        <v>-8.342423624536918</v>
+        <v>-11.00240723879485</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.039074601820172</v>
       </c>
       <c r="E20">
-        <v>-26.10748797014462</v>
+        <v>-26.2371245955622</v>
       </c>
       <c r="F20">
-        <v>3.15109505565575</v>
+        <v>4.276398877577165</v>
       </c>
       <c r="G20">
-        <v>-8.632020216675745</v>
+        <v>-9.852323718452036</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.369471867436172</v>
       </c>
       <c r="E21">
-        <v>-26.42123423481805</v>
+        <v>-26.80360952307772</v>
       </c>
       <c r="F21">
-        <v>3.656946562106265</v>
+        <v>4.39534469406216</v>
       </c>
       <c r="G21">
-        <v>-8.218486731183223</v>
+        <v>-9.038651214718884</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.710082184892439</v>
       </c>
       <c r="E22">
-        <v>-27.67602909760343</v>
+        <v>-26.16249081544179</v>
       </c>
       <c r="F22">
-        <v>3.470886456336777</v>
+        <v>3.585804908678809</v>
       </c>
       <c r="G22">
-        <v>-6.476388283689165</v>
+        <v>-7.885849736488333</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.069500080768896</v>
       </c>
       <c r="E23">
-        <v>-27.10203596018319</v>
+        <v>-27.71790842522637</v>
       </c>
       <c r="F23">
-        <v>3.831437696163468</v>
+        <v>4.145627529021584</v>
       </c>
       <c r="G23">
-        <v>-6.401695755232128</v>
+        <v>-8.010243485126448</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.457315379994878</v>
       </c>
       <c r="E24">
-        <v>-28.47897735237747</v>
+        <v>-27.04503605784865</v>
       </c>
       <c r="F24">
-        <v>3.873537350513594</v>
+        <v>4.398854186370774</v>
       </c>
       <c r="G24">
-        <v>-7.321305716221957</v>
+        <v>-8.19964972706477</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.892409942414315</v>
       </c>
       <c r="E25">
-        <v>-28.23914484045724</v>
+        <v>-28.19618320754647</v>
       </c>
       <c r="F25">
-        <v>3.629149355878471</v>
+        <v>4.247653031506024</v>
       </c>
       <c r="G25">
-        <v>-6.031328473026164</v>
+        <v>-7.157367501117248</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.384140136925382</v>
       </c>
       <c r="E26">
-        <v>-29.199566250374</v>
+        <v>-29.56941577952846</v>
       </c>
       <c r="F26">
-        <v>4.000270248984805</v>
+        <v>4.260663175601359</v>
       </c>
       <c r="G26">
-        <v>-6.794637647470382</v>
+        <v>-7.456435564043928</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.939018570239937</v>
       </c>
       <c r="E27">
-        <v>-27.98370720710658</v>
+        <v>-27.31598824314959</v>
       </c>
       <c r="F27">
-        <v>3.906871192621764</v>
+        <v>4.087226789683839</v>
       </c>
       <c r="G27">
-        <v>-6.474315882181581</v>
+        <v>-6.563780064834845</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.56897435987115</v>
       </c>
       <c r="E28">
-        <v>-27.87775450074911</v>
+        <v>-28.27365634086969</v>
       </c>
       <c r="F28">
-        <v>3.831794029994441</v>
+        <v>4.81012835925716</v>
       </c>
       <c r="G28">
-        <v>-6.891997481234808</v>
+        <v>-7.655482114592608</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.278022020745042</v>
       </c>
       <c r="E29">
-        <v>-28.2846424188123</v>
+        <v>-29.26867076373106</v>
       </c>
       <c r="F29">
-        <v>3.931209585130237</v>
+        <v>4.170003930472028</v>
       </c>
       <c r="G29">
-        <v>-6.640104692242742</v>
+        <v>-5.841227016524594</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.066824030677828</v>
       </c>
       <c r="E30">
-        <v>-28.07782248240799</v>
+        <v>-28.66741621278465</v>
       </c>
       <c r="F30">
-        <v>4.016607759208479</v>
+        <v>3.753175700940196</v>
       </c>
       <c r="G30">
-        <v>-6.029822174805796</v>
+        <v>-6.104332623258172</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.929244781125238</v>
       </c>
       <c r="E31">
-        <v>-29.01184288886004</v>
+        <v>-27.73635742833361</v>
       </c>
       <c r="F31">
-        <v>3.664288622730242</v>
+        <v>3.894323490653737</v>
       </c>
       <c r="G31">
-        <v>-6.059497905019822</v>
+        <v>-6.665225111794732</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.8650417344857</v>
       </c>
       <c r="E32">
-        <v>-28.20375481608729</v>
+        <v>-28.16831950697727</v>
       </c>
       <c r="F32">
-        <v>3.838151025539015</v>
+        <v>3.929961624868871</v>
       </c>
       <c r="G32">
-        <v>-5.829424921677092</v>
+        <v>-6.475352082935372</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.863279626868983</v>
       </c>
       <c r="E33">
-        <v>-27.58661890679598</v>
+        <v>-27.36579240028595</v>
       </c>
       <c r="F33">
-        <v>3.622858875982346</v>
+        <v>3.724130534451037</v>
       </c>
       <c r="G33">
-        <v>-6.428279435912476</v>
+        <v>-6.380852560516876</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.915425614104122</v>
       </c>
       <c r="E34">
-        <v>-28.28206118862793</v>
+        <v>-29.15291843962099</v>
       </c>
       <c r="F34">
-        <v>3.783654121282829</v>
+        <v>3.598235416409093</v>
       </c>
       <c r="G34">
-        <v>-5.248258652258036</v>
+        <v>-6.630424657085913</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.01490314500133</v>
       </c>
       <c r="E35">
-        <v>-27.60263159088711</v>
+        <v>-27.12932454455342</v>
       </c>
       <c r="F35">
-        <v>3.376762062664464</v>
+        <v>3.603879744291719</v>
       </c>
       <c r="G35">
-        <v>-6.095010127019584</v>
+        <v>-5.84988078256425</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.153231324024651</v>
       </c>
       <c r="E36">
-        <v>-27.16892152127649</v>
+        <v>-28.82805477125874</v>
       </c>
       <c r="F36">
-        <v>3.396084858538741</v>
+        <v>3.767758465009563</v>
       </c>
       <c r="G36">
-        <v>-6.701190878533374</v>
+        <v>-6.556347890099182</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.320321090773554</v>
       </c>
       <c r="E37">
-        <v>-27.52150397903969</v>
+        <v>-26.8193595556764</v>
       </c>
       <c r="F37">
-        <v>3.769220225569513</v>
+        <v>3.765930868383145</v>
       </c>
       <c r="G37">
-        <v>-6.231838284703202</v>
+        <v>-6.762687572470876</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.506990168596352</v>
       </c>
       <c r="E38">
-        <v>-26.03874120623418</v>
+        <v>-27.94905079552587</v>
       </c>
       <c r="F38">
-        <v>3.485180985929533</v>
+        <v>3.969614453579644</v>
       </c>
       <c r="G38">
-        <v>-6.134485072029854</v>
+        <v>-6.411256610749543</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.709101640996403</v>
       </c>
       <c r="E39">
-        <v>-25.92956422638326</v>
+        <v>-26.24712346617114</v>
       </c>
       <c r="F39">
-        <v>3.667128207436625</v>
+        <v>3.909531818559702</v>
       </c>
       <c r="G39">
-        <v>-6.755927438479684</v>
+        <v>-6.392727487366242</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.918498733923553</v>
       </c>
       <c r="E40">
-        <v>-25.48937391046766</v>
+        <v>-27.45212775724218</v>
       </c>
       <c r="F40">
-        <v>3.222040329549691</v>
+        <v>3.955003182803799</v>
       </c>
       <c r="G40">
-        <v>-6.016407844280669</v>
+        <v>-7.418198763065346</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.137384771078326</v>
       </c>
       <c r="E41">
-        <v>-25.50757837597849</v>
+        <v>-27.53233608886604</v>
       </c>
       <c r="F41">
-        <v>3.733141821109887</v>
+        <v>4.262641224289743</v>
       </c>
       <c r="G41">
-        <v>-7.168219469394979</v>
+        <v>-7.34622750304159</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.368737004001697</v>
       </c>
       <c r="E42">
-        <v>-25.10978816219671</v>
+        <v>-24.98525512698578</v>
       </c>
       <c r="F42">
-        <v>3.304918827516468</v>
+        <v>4.298044970029392</v>
       </c>
       <c r="G42">
-        <v>-6.78924145824137</v>
+        <v>-8.501369536968408</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.616874538344599</v>
       </c>
       <c r="E43">
-        <v>-24.25351712598236</v>
+        <v>-23.52378523896433</v>
       </c>
       <c r="F43">
-        <v>3.34146759263298</v>
+        <v>4.114499789253622</v>
       </c>
       <c r="G43">
-        <v>-6.684373307193876</v>
+        <v>-7.002036704414643</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.884805430526699</v>
       </c>
       <c r="E44">
-        <v>-24.34940303462077</v>
+        <v>-23.8380296357786</v>
       </c>
       <c r="F44">
-        <v>3.571120787430854</v>
+        <v>4.164098291113354</v>
       </c>
       <c r="G44">
-        <v>-7.079506780579129</v>
+        <v>-7.888776258745049</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.180922943884076</v>
       </c>
       <c r="E45">
-        <v>-23.6099032291682</v>
+        <v>-24.16872597866274</v>
       </c>
       <c r="F45">
-        <v>3.718464034685594</v>
+        <v>3.922641736127709</v>
       </c>
       <c r="G45">
-        <v>-7.314406539318115</v>
+        <v>-8.365978156048833</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.513386360875651</v>
       </c>
       <c r="E46">
-        <v>-22.43011800984587</v>
+        <v>-23.45381125859781</v>
       </c>
       <c r="F46">
-        <v>3.532717502687363</v>
+        <v>3.840572511883722</v>
       </c>
       <c r="G46">
-        <v>-7.327092549824603</v>
+        <v>-8.117091342406425</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.880793353089487</v>
       </c>
       <c r="E47">
-        <v>-21.63186578261779</v>
+        <v>-22.46395476763119</v>
       </c>
       <c r="F47">
-        <v>3.944750270707245</v>
+        <v>3.87921651992636</v>
       </c>
       <c r="G47">
-        <v>-7.721871794837153</v>
+        <v>-8.632871026879338</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.289405412450964</v>
       </c>
       <c r="E48">
-        <v>-22.37232562455998</v>
+        <v>-21.34855992022392</v>
       </c>
       <c r="F48">
-        <v>3.857960019129332</v>
+        <v>4.025671308162538</v>
       </c>
       <c r="G48">
-        <v>-7.611081077819903</v>
+        <v>-8.235347339614732</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.740535930180759</v>
       </c>
       <c r="E49">
-        <v>-21.68464514717719</v>
+        <v>-22.03378596469456</v>
       </c>
       <c r="F49">
-        <v>3.996415508786626</v>
+        <v>4.254559573003255</v>
       </c>
       <c r="G49">
-        <v>-8.186371128906753</v>
+        <v>-9.37767425175903</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.233525754677879</v>
       </c>
       <c r="E50">
-        <v>-20.16343563004655</v>
+        <v>-21.19618129833982</v>
       </c>
       <c r="F50">
-        <v>4.277095708179958</v>
+        <v>4.633008273380328</v>
       </c>
       <c r="G50">
-        <v>-7.594819678131003</v>
+        <v>-8.749432024771536</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.756992402184107</v>
       </c>
       <c r="E51">
-        <v>-20.24968041752263</v>
+        <v>-21.01150107135901</v>
       </c>
       <c r="F51">
-        <v>4.026729223714052</v>
+        <v>4.30459834510748</v>
       </c>
       <c r="G51">
-        <v>-8.569841550357152</v>
+        <v>-9.343717986162725</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.30755204686281</v>
       </c>
       <c r="E52">
-        <v>-19.2248097655287</v>
+        <v>-19.45716576686227</v>
       </c>
       <c r="F52">
-        <v>4.04746151785307</v>
+        <v>4.725849865261134</v>
       </c>
       <c r="G52">
-        <v>-7.689809161289311</v>
+        <v>-9.05052614156825</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.876333304878433</v>
       </c>
       <c r="E53">
-        <v>-19.94317518278747</v>
+        <v>-19.54531251342157</v>
       </c>
       <c r="F53">
-        <v>3.564371032819252</v>
+        <v>5.28715483434076</v>
       </c>
       <c r="G53">
-        <v>-8.332376118825231</v>
+        <v>-10.07809961368479</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.447001569789435</v>
       </c>
       <c r="E54">
-        <v>-18.90122312683661</v>
+        <v>-19.3430029371289</v>
       </c>
       <c r="F54">
-        <v>3.744063057102758</v>
+        <v>4.935122348633218</v>
       </c>
       <c r="G54">
-        <v>-8.71316168784328</v>
+        <v>-10.35569216769822</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.00606802132962</v>
       </c>
       <c r="E55">
-        <v>-17.85879558111494</v>
+        <v>-17.89499620233225</v>
       </c>
       <c r="F55">
-        <v>3.700184901009592</v>
+        <v>4.573962965734998</v>
       </c>
       <c r="G55">
-        <v>-9.614398121090154</v>
+        <v>-10.27074356916052</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.54239004406983</v>
       </c>
       <c r="E56">
-        <v>-17.53025479185845</v>
+        <v>-17.5836545573569</v>
       </c>
       <c r="F56">
-        <v>3.916362342172992</v>
+        <v>4.446154730947204</v>
       </c>
       <c r="G56">
-        <v>-9.122268973949797</v>
+        <v>-10.87934764000906</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.04783331713448</v>
       </c>
       <c r="E57">
-        <v>-16.67512493109403</v>
+        <v>-18.67304237853811</v>
       </c>
       <c r="F57">
-        <v>4.482127027110496</v>
+        <v>4.74172810076933</v>
       </c>
       <c r="G57">
-        <v>-9.598547229048124</v>
+        <v>-9.781600534096585</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.50414694994181</v>
       </c>
       <c r="E58">
-        <v>-17.20696250397686</v>
+        <v>-18.05563928928035</v>
       </c>
       <c r="F58">
-        <v>3.826786351889822</v>
+        <v>4.181115211174751</v>
       </c>
       <c r="G58">
-        <v>-9.246841492047032</v>
+        <v>-11.28465773038203</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.91048313809309</v>
       </c>
       <c r="E59">
-        <v>-15.89181213961725</v>
+        <v>-16.28656374733988</v>
       </c>
       <c r="F59">
-        <v>3.881725110096416</v>
+        <v>5.000359946407915</v>
       </c>
       <c r="G59">
-        <v>-8.580044651709187</v>
+        <v>-11.10258765735873</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.26208922769314</v>
       </c>
       <c r="E60">
-        <v>-17.01067126964038</v>
+        <v>-17.95882504347037</v>
       </c>
       <c r="F60">
-        <v>3.820502206817358</v>
+        <v>4.608467166514678</v>
       </c>
       <c r="G60">
-        <v>-9.768795343950684</v>
+        <v>-10.91896162793198</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.55824949937225</v>
       </c>
       <c r="E61">
-        <v>-16.8721769490638</v>
+        <v>-16.22230017269703</v>
       </c>
       <c r="F61">
-        <v>3.908648110658887</v>
+        <v>4.551738820623637</v>
       </c>
       <c r="G61">
-        <v>-9.857504722220995</v>
+        <v>-11.51241333184727</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.79479296878458</v>
       </c>
       <c r="E62">
-        <v>-17.30808785704215</v>
+        <v>-16.26423384200806</v>
       </c>
       <c r="F62">
-        <v>3.8779384692526</v>
+        <v>4.121784836464643</v>
       </c>
       <c r="G62">
-        <v>-9.808598032969343</v>
+        <v>-11.69559574817176</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.9755413770218</v>
       </c>
       <c r="E63">
-        <v>-14.94548786928636</v>
+        <v>-15.99502964767408</v>
       </c>
       <c r="F63">
-        <v>3.891091146880325</v>
+        <v>4.549607152461455</v>
       </c>
       <c r="G63">
-        <v>-9.18134565909809</v>
+        <v>-11.98855254403295</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.10675334488789</v>
       </c>
       <c r="E64">
-        <v>-15.05206097658287</v>
+        <v>-14.65678406587535</v>
       </c>
       <c r="F64">
-        <v>3.970854495311433</v>
+        <v>4.9239398011643</v>
       </c>
       <c r="G64">
-        <v>-10.54153957318183</v>
+        <v>-12.7163826019328</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.18696180665845</v>
       </c>
       <c r="E65">
-        <v>-14.67720295517594</v>
+        <v>-15.8914272193266</v>
       </c>
       <c r="F65">
-        <v>4.024504116902859</v>
+        <v>4.341164530989062</v>
       </c>
       <c r="G65">
-        <v>-9.875494226681395</v>
+        <v>-10.99311453746611</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.22293311290267</v>
       </c>
       <c r="E66">
-        <v>-15.19971640007697</v>
+        <v>-16.18618559248586</v>
       </c>
       <c r="F66">
-        <v>4.173662291136693</v>
+        <v>4.342209776893251</v>
       </c>
       <c r="G66">
-        <v>-9.829947741152102</v>
+        <v>-10.85924269694906</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.21652197499313</v>
       </c>
       <c r="E67">
-        <v>-14.84671732270506</v>
+        <v>-14.28017352502745</v>
       </c>
       <c r="F67">
-        <v>3.98044700204125</v>
+        <v>4.672147981374498</v>
       </c>
       <c r="G67">
-        <v>-11.14251283656234</v>
+        <v>-11.25309167866508</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.17878833212471</v>
       </c>
       <c r="E68">
-        <v>-13.37652106527083</v>
+        <v>-16.76225277100161</v>
       </c>
       <c r="F68">
-        <v>3.500001305886215</v>
+        <v>4.554445374033123</v>
       </c>
       <c r="G68">
-        <v>-9.920977811845441</v>
+        <v>-11.98037218600541</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.10762373512015</v>
       </c>
       <c r="E69">
-        <v>-14.52682591880323</v>
+        <v>-14.38772478270962</v>
       </c>
       <c r="F69">
-        <v>3.838217541187463</v>
+        <v>3.67604763915238</v>
       </c>
       <c r="G69">
-        <v>-10.30046233646656</v>
+        <v>-11.28322426416353</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.00953435040304</v>
       </c>
       <c r="E70">
-        <v>-14.73613651591176</v>
+        <v>-15.42240863787817</v>
       </c>
       <c r="F70">
-        <v>3.68736480162411</v>
+        <v>4.7026438224822</v>
       </c>
       <c r="G70">
-        <v>-10.78199442733571</v>
+        <v>-11.04365994675971</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.88912967667144</v>
       </c>
       <c r="E71">
-        <v>-14.53774406963572</v>
+        <v>-15.46385323199637</v>
       </c>
       <c r="F71">
-        <v>3.600541292221973</v>
+        <v>3.465053667450213</v>
       </c>
       <c r="G71">
-        <v>-10.28579330918205</v>
+        <v>-11.17282750206545</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.75146570054405</v>
       </c>
       <c r="E72">
-        <v>-15.50599973958576</v>
+        <v>-14.64142348204133</v>
       </c>
       <c r="F72">
-        <v>3.882480537818081</v>
+        <v>3.805110169025202</v>
       </c>
       <c r="G72">
-        <v>-10.19142620858512</v>
+        <v>-11.24798681744352</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.59814308343656</v>
       </c>
       <c r="E73">
-        <v>-14.81796151275635</v>
+        <v>-14.76015101357443</v>
       </c>
       <c r="F73">
-        <v>3.444589019610905</v>
+        <v>3.750730459006758</v>
       </c>
       <c r="G73">
-        <v>-10.50163425725145</v>
+        <v>-9.830566813167946</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.43049563795517</v>
       </c>
       <c r="E74">
-        <v>-14.70281600416332</v>
+        <v>-13.54387987917231</v>
       </c>
       <c r="F74">
-        <v>2.815192614696959</v>
+        <v>3.479520820987752</v>
       </c>
       <c r="G74">
-        <v>-10.34983912318479</v>
+        <v>-10.55822472269975</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.25911171185449</v>
       </c>
       <c r="E75">
-        <v>-15.03073639248075</v>
+        <v>-14.17038520118549</v>
       </c>
       <c r="F75">
-        <v>3.514270496184325</v>
+        <v>3.766843082990439</v>
       </c>
       <c r="G75">
-        <v>-9.516660885134252</v>
+        <v>-11.14701186795021</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.0813788313074</v>
       </c>
       <c r="E76">
-        <v>-15.17696534666244</v>
+        <v>-13.79600719802336</v>
       </c>
       <c r="F76">
-        <v>3.226761356883617</v>
+        <v>3.242205656970982</v>
       </c>
       <c r="G76">
-        <v>-9.251913247813196</v>
+        <v>-10.71130765898119</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.90499204433312</v>
       </c>
       <c r="E77">
-        <v>-16.49271346959106</v>
+        <v>-16.59012094549605</v>
       </c>
       <c r="F77">
-        <v>3.0867649213706</v>
+        <v>3.212924518300422</v>
       </c>
       <c r="G77">
-        <v>-9.841157248348074</v>
+        <v>-10.52192790140718</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.7307676080759</v>
       </c>
       <c r="E78">
-        <v>-16.28859703216932</v>
+        <v>-17.67632977792388</v>
       </c>
       <c r="F78">
-        <v>3.125454856884786</v>
+        <v>3.528283126124133</v>
       </c>
       <c r="G78">
-        <v>-8.460424709738701</v>
+        <v>-10.80072549399691</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.57043600253774</v>
       </c>
       <c r="E79">
-        <v>-16.53015942116048</v>
+        <v>-17.00308607567753</v>
       </c>
       <c r="F79">
-        <v>3.068964066881061</v>
+        <v>3.362374094422696</v>
       </c>
       <c r="G79">
-        <v>-9.429136682167</v>
+        <v>-9.974807282313991</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.42321347747045</v>
       </c>
       <c r="E80">
-        <v>-16.05020457498354</v>
+        <v>-17.3199886867343</v>
       </c>
       <c r="F80">
-        <v>3.254032772747484</v>
+        <v>3.625060227204806</v>
       </c>
       <c r="G80">
-        <v>-9.038386371075743</v>
+        <v>-8.862053473472002</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.29228320525288</v>
       </c>
       <c r="E81">
-        <v>-16.7848589132479</v>
+        <v>-18.05735558092926</v>
       </c>
       <c r="F81">
-        <v>3.364659382058675</v>
+        <v>3.3860489141526</v>
       </c>
       <c r="G81">
-        <v>-8.75250090048644</v>
+        <v>-8.893576488096944</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.18376304074058</v>
       </c>
       <c r="E82">
-        <v>-19.77166828669497</v>
+        <v>-18.15068290175334</v>
       </c>
       <c r="F82">
-        <v>3.144137835569225</v>
+        <v>3.451117055394346</v>
       </c>
       <c r="G82">
-        <v>-8.484647971449549</v>
+        <v>-9.124050047449925</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.09577800651895</v>
       </c>
       <c r="E83">
-        <v>-19.18555695283021</v>
+        <v>-17.76188623735079</v>
       </c>
       <c r="F83">
-        <v>2.964976352767391</v>
+        <v>3.125941054600826</v>
       </c>
       <c r="G83">
-        <v>-8.424528464456383</v>
+        <v>-9.120868613186685</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.02750372416012</v>
       </c>
       <c r="E84">
-        <v>-20.25844301472748</v>
+        <v>-19.52088139615019</v>
       </c>
       <c r="F84">
-        <v>2.757547303080879</v>
+        <v>2.928840934894809</v>
       </c>
       <c r="G84">
-        <v>-7.755351341875802</v>
+        <v>-8.114370073973145</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.97183468962054</v>
       </c>
       <c r="E85">
-        <v>-21.88311457751135</v>
+        <v>-21.64995250780442</v>
       </c>
       <c r="F85">
-        <v>2.713414170335328</v>
+        <v>3.771253703964938</v>
       </c>
       <c r="G85">
-        <v>-8.614560399501627</v>
+        <v>-8.121603615976452</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.93130445105479</v>
       </c>
       <c r="E86">
-        <v>-21.93127037010892</v>
+        <v>-22.52982142207275</v>
       </c>
       <c r="F86">
-        <v>2.853478705202708</v>
+        <v>3.351722088435451</v>
       </c>
       <c r="G86">
-        <v>-7.983583661898697</v>
+        <v>-7.064887411477707</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.89398911181884</v>
       </c>
       <c r="E87">
-        <v>-22.67125472228031</v>
+        <v>-22.99407604886511</v>
       </c>
       <c r="F87">
-        <v>2.644695586958495</v>
+        <v>3.502966003359918</v>
       </c>
       <c r="G87">
-        <v>-7.734865686078792</v>
+        <v>-8.00428119261022</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.85408250555259</v>
       </c>
       <c r="E88">
-        <v>-24.26407752736824</v>
+        <v>-23.44038433316507</v>
       </c>
       <c r="F88">
-        <v>2.61945131466639</v>
+        <v>3.19325647453658</v>
       </c>
       <c r="G88">
-        <v>-7.178094826738625</v>
+        <v>-7.313559039660062</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.80369689340967</v>
       </c>
       <c r="E89">
-        <v>-26.83401822603923</v>
+        <v>-26.23437128336554</v>
       </c>
       <c r="F89">
-        <v>2.860708322706689</v>
+        <v>3.18415808405238</v>
       </c>
       <c r="G89">
-        <v>-6.731363190578292</v>
+        <v>-7.490133607088169</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.73763509610263</v>
       </c>
       <c r="E90">
-        <v>-28.07137846389507</v>
+        <v>-26.84352802145533</v>
       </c>
       <c r="F90">
-        <v>2.273527182674698</v>
+        <v>3.498941806628786</v>
       </c>
       <c r="G90">
-        <v>-7.25374410285651</v>
+        <v>-8.410481819733256</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.64521069750398</v>
       </c>
       <c r="E91">
-        <v>-29.20872735329152</v>
+        <v>-29.58293327444136</v>
       </c>
       <c r="F91">
-        <v>2.686044564704703</v>
+        <v>3.112492223966914</v>
       </c>
       <c r="G91">
-        <v>-7.104501399400626</v>
+        <v>-7.135494726739283</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.51565593007502</v>
       </c>
       <c r="E92">
-        <v>-30.82677828707619</v>
+        <v>-30.45993340042582</v>
       </c>
       <c r="F92">
-        <v>2.593868129308381</v>
+        <v>3.519187903051764</v>
       </c>
       <c r="G92">
-        <v>-7.663549914071812</v>
+        <v>-8.609650860466889</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.34634791169897</v>
       </c>
       <c r="E93">
-        <v>-33.46977685691292</v>
+        <v>-33.49277471216087</v>
       </c>
       <c r="F93">
-        <v>2.542890219596301</v>
+        <v>3.176592720894326</v>
       </c>
       <c r="G93">
-        <v>-6.99751118866246</v>
+        <v>-6.73314426407842</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.12716462143825</v>
       </c>
       <c r="E94">
-        <v>-34.18377003251728</v>
+        <v>-33.74729985799898</v>
       </c>
       <c r="F94">
-        <v>2.284695476790377</v>
+        <v>2.917134180767881</v>
       </c>
       <c r="G94">
-        <v>-7.19723971159223</v>
+        <v>-7.484307046939052</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.855904603820097</v>
       </c>
       <c r="E95">
-        <v>-36.64602588352287</v>
+        <v>-36.64998829827957</v>
       </c>
       <c r="F95">
-        <v>2.278021740062715</v>
+        <v>2.905820185707982</v>
       </c>
       <c r="G95">
-        <v>-7.100184448017417</v>
+        <v>-6.880675415490501</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.523337100584323</v>
       </c>
       <c r="E96">
-        <v>-38.57112773316062</v>
+        <v>-38.7037825865043</v>
       </c>
       <c r="F96">
-        <v>2.216535941601694</v>
+        <v>2.920966749083244</v>
       </c>
       <c r="G96">
-        <v>-6.94849856195355</v>
+        <v>-6.835953255800487</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.1414729908995</v>
       </c>
       <c r="E97">
-        <v>-40.21541438110872</v>
+        <v>-40.80087135047937</v>
       </c>
       <c r="F97">
-        <v>2.315108965190476</v>
+        <v>2.938233894679281</v>
       </c>
       <c r="G97">
-        <v>-6.50138952360174</v>
+        <v>-6.818317979712789</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.702922469843225</v>
       </c>
       <c r="E98">
-        <v>-42.75993222670063</v>
+        <v>-43.28985878355223</v>
       </c>
       <c r="F98">
-        <v>2.292606087837997</v>
+        <v>2.325022964221127</v>
       </c>
       <c r="G98">
-        <v>-7.662526955500177</v>
+        <v>-7.47604723581857</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.22537866184517</v>
       </c>
       <c r="E99">
-        <v>-45.64909411512032</v>
+        <v>-43.96600070916348</v>
       </c>
       <c r="F99">
-        <v>1.943734679137672</v>
+        <v>2.461316695303846</v>
       </c>
       <c r="G99">
-        <v>-6.660269225122443</v>
+        <v>-6.678993670692561</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.701698658925468</v>
       </c>
       <c r="E100">
-        <v>-47.63314084667891</v>
+        <v>-46.51745164846115</v>
       </c>
       <c r="F100">
-        <v>2.145258089465511</v>
+        <v>2.569317520207238</v>
       </c>
       <c r="G100">
-        <v>-7.379508417347884</v>
+        <v>-7.981517881482191</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.174861260143761</v>
       </c>
       <c r="E101">
-        <v>-48.85112940484844</v>
+        <v>-49.51506482877203</v>
       </c>
       <c r="F101">
-        <v>1.906698132599205</v>
+        <v>2.437774906870838</v>
       </c>
       <c r="G101">
-        <v>-7.282910009057489</v>
+        <v>-6.936269406731483</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.605361868519045</v>
       </c>
       <c r="E102">
-        <v>-51.703610653806</v>
+        <v>-51.12606266428974</v>
       </c>
       <c r="F102">
-        <v>2.105210917981793</v>
+        <v>2.074285892571007</v>
       </c>
       <c r="G102">
-        <v>-6.827991393778539</v>
+        <v>-7.642332627710623</v>
       </c>
     </row>
   </sheetData>
